--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>121390513</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,6 +942,138 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121446763</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Nyplan, Nyplan, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>615218</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6565891</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>121390513</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>121446763</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>4775</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>121390513</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>121390513</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1074,6 +1074,123 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121632913</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nyplan, Nyplan, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>615250</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6565892</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Staffan Petré</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53489-2024 artfynd.xlsx
+++ b/artfynd/A 53489-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121372699</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>121390513</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>121446763</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>4776</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>121632913</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
